--- a/forms/trg/Formulir_TRG_ncprg.xlsx
+++ b/forms/trg/Formulir_TRG_ncprg.xlsx
@@ -783,7 +783,7 @@
         </is>
       </c>
       <c r="B25" s="7">
-        <f>COUNTA(Anggota!B5:B24)</f>
+        <f>COUNTA(Anggota!B5:B25)</f>
         <v/>
       </c>
     </row>
@@ -794,7 +794,7 @@
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!F5:F24)</f>
+        <f>COUNTA(Anggota!F5:F25)</f>
         <v/>
       </c>
     </row>
@@ -820,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M24"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -925,24 +925,16 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Dr. Eng Achmad Yasir Baeda, ST.,MT.</t>
-        </is>
-      </c>
-      <c r="C5" s="11" t="inlineStr">
-        <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
+          <t>Prof. Dr. Mahatma Lanuru, ST, M.Sc</t>
+        </is>
+      </c>
+      <c r="C5" s="12" t="n"/>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
-      <c r="E5" s="11" t="inlineStr">
-        <is>
-          <t>Achmad Yasir Baeda is a senior lecturer in Design Coastal Protection and Natural Ocean-Coastal Hazards at the Department of Ocean Engineering, Faculty of Engineering, Hasanuddin University, Indonesia. He completed his B.Sc in Naval Architecture and Shipbuilding Engineering at Hasanuddin University, continued his Master\'s at Ocean Technology of Sepuluh Nopember Institute Technology, and completed his Doctoral Study at Tsunami Engineering, Hiroshima University, Japan, in 2010. His main research topics are coastal oceanography, coastal protection design, ocean coastal Hazard Mitigation, and weather anomalies. He recently conducted modeling on tsunami mitigation schemes at Awerange Port of Barru and several weather anomalies modeling at the Indonesian Archipelago, especially at Makassar Strait.</t>
-        </is>
-      </c>
+          <t>Mahatma Lanuru is an oceanography and sediment dynamics professor at the Department of Marine Science, Faculty of Marine Science and Fisheries, Hasanuddin University, Indonesia. He completed his B.Sc in Marine Science at the Hasanuddin University, continued his Master\'s at the Aarhus University (Denmark), and completed his Ph.D. at the University of Kiel, Germany, in 2004. His main research topics are coastal oceanography, sediment dynamics (erosion/deposition), and habitat restoration. He recently conducted seagrass transplantation experiments to assess the feasibility of using seagrass for coastal protection and developing a \"hybrid\" shoreline stabilization technique to prevent and reduce the risk of coastal and small island erosions in Indonesia.</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
@@ -962,12 +954,12 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Ir. Mardiana E. Fachri, MS.</t>
+          <t>Dr. Eng Achmad Yasir Baeda, ST.,MT.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
@@ -975,7 +967,11 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E6" s="11" t="n"/>
+      <c r="E6" s="11" t="inlineStr">
+        <is>
+          <t>Achmad Yasir Baeda is a senior lecturer in Design Coastal Protection and Natural Ocean-Coastal Hazards at the Department of Ocean Engineering, Faculty of Engineering, Hasanuddin University, Indonesia. He completed his B.Sc in Naval Architecture and Shipbuilding Engineering at Hasanuddin University, continued his Master\'s at Ocean Technology of Sepuluh Nopember Institute Technology, and completed his Doctoral Study at Tsunami Engineering, Hiroshima University, Japan, in 2010. His main research topics are coastal oceanography, coastal protection design, ocean coastal Hazard Mitigation, and weather anomalies. He recently conducted modeling on tsunami mitigation schemes at Awerange Port of Barru and several weather anomalies modeling at the Indonesian Archipelago, especially at Makassar Strait.</t>
+        </is>
+      </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
@@ -995,12 +991,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Amran Saru, ST., M.Si.</t>
+          <t>Prof. Dr. Ir. Mardiana E. Fachri, MS.</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1028,12 +1024,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr. Wasir Samad, S.Si., M.Si.</t>
+          <t>Prof. Dr. Amran Saru, ST., M.Si.</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1041,11 +1037,7 @@
           <t>Hasanuddin University</t>
         </is>
       </c>
-      <c r="E8" s="11" t="inlineStr">
-        <is>
-          <t>Physical Oceanographic and Marine Hydrodynamics</t>
-        </is>
-      </c>
+      <c r="E8" s="11" t="n"/>
       <c r="F8" s="12" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="12" t="n"/>
@@ -1065,16 +1057,24 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Paul Simon Kench</t>
+          <t>Dr. Wasir Samad, S.Si., M.Si.</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Physical Oceanographic and Marine Hydrodynamics</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Mustono, S.Kel, M.Si</t>
+          <t>Prof. Dr. Paul Simon Kench</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
+          <t>External collaborator</t>
         </is>
       </c>
       <c r="D10" s="12" t="n"/>
@@ -1123,19 +1123,15 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Muhammad Azizir Furkhan D., S. Kel</t>
+          <t>Mustono, S.Kel, M.Si</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n"/>
       <c r="E11" s="11" t="n"/>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
@@ -1156,15 +1152,19 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Supardi</t>
+          <t>Muhammad Azizir Furkhan D., S. Kel</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="12" t="n"/>
       <c r="G12" s="12" t="n"/>
@@ -1183,10 +1183,22 @@
       <c r="A13" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>Supardi</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
       <c r="D13" s="12" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>Coastlines are among the most dynamic environments on Earth. They are constantly shaped by waves, winds, tides, and storms. Sea level rise, warmer waters, and changes in storm patterns are already impacting coastal areas, leading to various issues such as the flooding of low-lying areas, erosion, saltwater intrusion, and the loss of wetlands.</t>
+        </is>
+      </c>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
       <c r="H13" s="12" t="n"/>
@@ -1194,7 +1206,11 @@
       <c r="J13" s="12" t="n"/>
       <c r="K13" s="12" t="n"/>
       <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
+      <c r="M13" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -1383,15 +1399,32 @@
       <c r="L24" s="12" t="n"/>
       <c r="M24" s="12" t="n"/>
     </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>

--- a/forms/trg/Formulir_TRG_ncprg.xlsx
+++ b/forms/trg/Formulir_TRG_ncprg.xlsx
@@ -928,7 +928,11 @@
           <t>Prof. Dr. Mahatma Lanuru, ST, M.Sc</t>
         </is>
       </c>
-      <c r="C5" s="12" t="n"/>
+      <c r="C5" s="11" t="inlineStr">
+        <is>
+          <t>Leader</t>
+        </is>
+      </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Mahatma Lanuru is an oceanography and sediment dynamics professor at the Department of Marine Science, Faculty of Marine Science and Fisheries, Hasanuddin University, Indonesia. He completed his B.Sc in Marine Science at the Hasanuddin University, continued his Master\'s at the Aarhus University (Denmark), and completed his Ph.D. at the University of Kiel, Germany, in 2004. His main research topics are coastal oceanography, sediment dynamics (erosion/deposition), and habitat restoration. He recently conducted seagrass transplantation experiments to assess the feasibility of using seagrass for coastal protection and developing a \"hybrid\" shoreline stabilization technique to prevent and reduce the risk of coastal and small island erosions in Indonesia.</t>
